--- a/Configs/Datas/#ZZZ.Skill.xlsx
+++ b/Configs/Datas/#ZZZ.Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE890CF-ED55-4656-99AD-D1276E08072F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C50ED3A-B2F4-424E-B642-8D2E1114E942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="75">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -216,15 +216,6 @@
     <t>基础_特殊冲刺起步_后</t>
   </si>
   <si>
-    <t>攻击_普通攻击_3_霜冻</t>
-  </si>
-  <si>
-    <t>攻击_特殊冲刺攻击_1</t>
-  </si>
-  <si>
-    <t>攻击_特殊冲刺攻击_2</t>
-  </si>
-  <si>
     <t>攻击_特殊技_2_强化</t>
   </si>
   <si>
@@ -232,11 +223,63 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CustomGauge01,2,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>#Remark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CustomGauge01,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_冲刺攻击_急冻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_普通攻击_1_急冻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_普通攻击_2_急冻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_普通攻击_3_急冻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_特殊技_3_急冻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_特殊冲刺攻击_蓄力前摇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_特殊冲刺攻击_蓄力前摇_快蓄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_特殊冲刺攻击_无蓄力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_特殊冲刺攻击_蓄力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_普通攻击_3_向前_近</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_普通攻击_3_向前_远</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_普通攻击_3_后撤_近</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_普通攻击_3_后撤_远</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -601,10 +644,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="24.125" customWidth="1"/>
+    <col min="4" max="4" width="29.375" customWidth="1"/>
     <col min="5" max="5" width="39.625" customWidth="1"/>
     <col min="6" max="6" width="41.875" customWidth="1"/>
   </cols>
@@ -614,7 +657,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -836,7 +879,7 @@
         <v>32</v>
       </c>
       <c r="F19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
@@ -850,7 +893,7 @@
         <v>33</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
@@ -1161,7 +1204,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
         <v>16</v>
       </c>
@@ -1172,172 +1215,169 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
         <v>17</v>
       </c>
       <c r="C50">
-        <v>10400</v>
+        <v>140000</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
         <v>17</v>
       </c>
       <c r="C51">
-        <v>10401</v>
+        <v>140010</v>
       </c>
       <c r="D51" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
         <v>17</v>
       </c>
       <c r="C52">
-        <v>10402</v>
+        <v>140020</v>
       </c>
       <c r="D52" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
         <v>17</v>
       </c>
       <c r="C53">
-        <v>10403</v>
+        <v>140030</v>
       </c>
       <c r="D53" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
         <v>17</v>
       </c>
       <c r="C54">
-        <v>10404</v>
+        <v>140040</v>
       </c>
       <c r="D54" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
         <v>17</v>
       </c>
       <c r="C55">
-        <v>10405</v>
+        <v>140050</v>
       </c>
       <c r="D55" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
         <v>17</v>
       </c>
       <c r="C56">
-        <v>10406</v>
+        <v>140060</v>
       </c>
       <c r="D56" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
         <v>17</v>
       </c>
       <c r="C57">
-        <v>10407</v>
+        <v>140070</v>
       </c>
       <c r="D57" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
         <v>17</v>
       </c>
       <c r="C58">
-        <v>10408</v>
+        <v>140080</v>
       </c>
       <c r="D58" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
         <v>17</v>
       </c>
       <c r="C59">
-        <v>10409</v>
+        <v>140090</v>
       </c>
       <c r="D59" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
         <v>17</v>
       </c>
       <c r="C60">
-        <v>10410</v>
+        <v>140100</v>
       </c>
       <c r="D60" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61">
+        <v>140110</v>
+      </c>
+      <c r="D61" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B62" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62">
+        <v>140120</v>
+      </c>
+      <c r="D62" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63">
+        <v>140130</v>
+      </c>
+      <c r="D63" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B64" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64">
+        <v>140140</v>
+      </c>
+      <c r="D64" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B61" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61">
-        <v>10411</v>
-      </c>
-      <c r="D61" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B62" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62">
-        <v>10412</v>
-      </c>
-      <c r="D62" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B63" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63">
-        <v>10413</v>
-      </c>
-      <c r="D63" t="s">
-        <v>58</v>
-      </c>
-      <c r="F63" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B64" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64">
-        <v>10414</v>
-      </c>
-      <c r="D64" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.2">
@@ -1345,10 +1385,10 @@
         <v>17</v>
       </c>
       <c r="C65">
-        <v>10415</v>
+        <v>140150</v>
       </c>
       <c r="D65" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.2">
@@ -1356,10 +1396,10 @@
         <v>17</v>
       </c>
       <c r="C66">
-        <v>10416</v>
+        <v>140160</v>
       </c>
       <c r="D66" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.2">
@@ -1367,10 +1407,10 @@
         <v>17</v>
       </c>
       <c r="C67">
-        <v>10417</v>
+        <v>140170</v>
       </c>
       <c r="D67" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.2">
@@ -1378,10 +1418,10 @@
         <v>17</v>
       </c>
       <c r="C68">
-        <v>10418</v>
+        <v>140180</v>
       </c>
       <c r="D68" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.2">
@@ -1389,10 +1429,10 @@
         <v>17</v>
       </c>
       <c r="C69">
-        <v>10419</v>
+        <v>140190</v>
       </c>
       <c r="D69" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.2">
@@ -1400,10 +1440,13 @@
         <v>17</v>
       </c>
       <c r="C70">
-        <v>10420</v>
+        <v>140200</v>
       </c>
       <c r="D70" t="s">
-        <v>41</v>
+        <v>63</v>
+      </c>
+      <c r="F70" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.2">
@@ -1411,10 +1454,13 @@
         <v>17</v>
       </c>
       <c r="C71">
-        <v>10421</v>
+        <v>140210</v>
       </c>
       <c r="D71" t="s">
-        <v>48</v>
+        <v>64</v>
+      </c>
+      <c r="F71" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.2">
@@ -1422,13 +1468,118 @@
         <v>17</v>
       </c>
       <c r="C72">
-        <v>10422</v>
+        <v>140220</v>
       </c>
       <c r="D72" t="s">
+        <v>65</v>
+      </c>
+      <c r="F72" t="s">
         <v>61</v>
       </c>
-      <c r="F72" t="s">
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B73" t="s">
+        <v>17</v>
+      </c>
+      <c r="C73">
+        <v>140230</v>
+      </c>
+      <c r="D73" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C74">
+        <v>140240</v>
+      </c>
+      <c r="D74" t="s">
+        <v>58</v>
+      </c>
+      <c r="F74" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B75" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75">
+        <v>140250</v>
+      </c>
+      <c r="D75" t="s">
+        <v>66</v>
+      </c>
+      <c r="F75" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B76" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76">
+        <v>140260</v>
+      </c>
+      <c r="D76" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B77" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77">
+        <v>140270</v>
+      </c>
+      <c r="D77" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B78" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78">
+        <v>140280</v>
+      </c>
+      <c r="D78" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B79" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79">
+        <v>140290</v>
+      </c>
+      <c r="D79" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B80" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80">
+        <v>140300</v>
+      </c>
+      <c r="D80" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B81" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81">
+        <v>140310</v>
+      </c>
+      <c r="D81" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/#ZZZ.Skill.xlsx
+++ b/Configs/Datas/#ZZZ.Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C50ED3A-B2F4-424E-B642-8D2E1114E942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74E2A65-BCC0-4807-8853-EE1C88646A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="76">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -280,6 +280,10 @@
   </si>
   <si>
     <t>攻击_普通攻击_3_后撤_远</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Energy,40,40</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1499,7 +1503,7 @@
         <v>58</v>
       </c>
       <c r="F74" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.2">
@@ -1513,7 +1517,7 @@
         <v>66</v>
       </c>
       <c r="F75" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.2">

--- a/Configs/Datas/#ZZZ.Skill.xlsx
+++ b/Configs/Datas/#ZZZ.Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74E2A65-BCC0-4807-8853-EE1C88646A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC59AF70-3FD9-436F-A634-D34AE0B0251F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="80">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,14 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>costs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(list),ZZZ.CostInfo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>技能消耗</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -219,18 +211,10 @@
     <t>攻击_特殊技_2_强化</t>
   </si>
   <si>
-    <t>Energy,200,200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>#Remark</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CustomGauge01,1,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>攻击_冲刺攻击_急冻</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -283,7 +267,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Energy,40,40</t>
+    <t>(list),ZZZ.AttributeCondition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>condition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Energy,GreaterEqual,40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_FlashFreeze,GreaterEqual,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Energy,FixedValue,40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_FlashFreeze,FixedValue,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list),ZZZ.AttributeCost</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -648,20 +664,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="29.375" customWidth="1"/>
     <col min="5" max="5" width="39.625" customWidth="1"/>
     <col min="6" max="6" width="41.875" customWidth="1"/>
+    <col min="7" max="7" width="42.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -673,10 +690,13 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+      <c r="G1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -690,900 +710,915 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+      <c r="G2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>10000</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>10001</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>10002</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8">
         <v>10003</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9">
         <v>10004</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10">
         <v>10005</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>10006</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12">
         <v>10007</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13">
         <v>10008</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14">
         <v>10009</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15">
         <v>10010</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16">
         <v>10011</v>
       </c>
       <c r="D16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17">
         <v>10012</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18">
         <v>10013</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19">
         <v>10014</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C20">
         <v>10015</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C21">
         <v>10016</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C22">
         <v>10017</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C23">
         <v>10018</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C24">
         <v>10019</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C25">
         <v>10020</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C26">
         <v>10021</v>
       </c>
       <c r="D26" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C27">
         <v>10022</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C28">
         <v>10023</v>
       </c>
       <c r="D28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C29">
         <v>10200</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C30">
         <v>10201</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C31">
         <v>10202</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C32">
         <v>10203</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C33">
         <v>10204</v>
       </c>
       <c r="D33" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C34">
         <v>10205</v>
       </c>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C35">
         <v>10206</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C36">
         <v>10207</v>
       </c>
       <c r="D36" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C37">
         <v>10208</v>
       </c>
       <c r="D37" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C38">
         <v>10209</v>
       </c>
       <c r="D38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C39">
         <v>10210</v>
       </c>
       <c r="D39" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C40">
         <v>10211</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C41">
         <v>10212</v>
       </c>
       <c r="D41" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C42">
         <v>10213</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C43">
         <v>10214</v>
       </c>
       <c r="D43" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C44">
         <v>10215</v>
       </c>
       <c r="D44" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C45">
         <v>10216</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C46">
         <v>10217</v>
       </c>
       <c r="D46" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C47">
         <v>10218</v>
       </c>
       <c r="D47" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C48">
         <v>10219</v>
       </c>
       <c r="D48" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C49">
         <v>10220</v>
       </c>
       <c r="D49" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C50">
         <v>140000</v>
       </c>
       <c r="D50" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C51">
         <v>140010</v>
       </c>
       <c r="D51" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C52">
         <v>140020</v>
       </c>
       <c r="D52" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C53">
         <v>140030</v>
       </c>
       <c r="D53" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C54">
         <v>140040</v>
       </c>
       <c r="D54" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C55">
         <v>140050</v>
       </c>
       <c r="D55" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C56">
         <v>140060</v>
       </c>
       <c r="D56" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C57">
         <v>140070</v>
       </c>
       <c r="D57" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C58">
         <v>140080</v>
       </c>
       <c r="D58" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C59">
         <v>140090</v>
       </c>
       <c r="D59" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C60">
         <v>140100</v>
       </c>
       <c r="D60" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C61">
         <v>140110</v>
       </c>
       <c r="D61" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C62">
         <v>140120</v>
       </c>
       <c r="D62" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C63">
         <v>140130</v>
       </c>
       <c r="D63" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C64">
         <v>140140</v>
       </c>
       <c r="D64" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C65">
         <v>140150</v>
       </c>
       <c r="D65" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C66">
         <v>140160</v>
       </c>
       <c r="D66" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C67">
         <v>140170</v>
       </c>
       <c r="D67" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C68">
         <v>140180</v>
       </c>
       <c r="D68" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C69">
         <v>140190</v>
       </c>
       <c r="D69" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C70">
         <v>140200</v>
       </c>
       <c r="D70" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F70" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="G70" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C71">
         <v>140210</v>
       </c>
       <c r="D71" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F71" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="G71" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C72">
         <v>140220</v>
       </c>
       <c r="D72" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F72" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="G72" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C73">
         <v>140230</v>
       </c>
       <c r="D73" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C74">
         <v>140240</v>
       </c>
       <c r="D74" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F74" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="G74" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C75">
         <v>140250</v>
       </c>
       <c r="D75" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F75" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="G75" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C76">
         <v>140260</v>
       </c>
       <c r="D76" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B77" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C77">
         <v>140270</v>
       </c>
       <c r="D77" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C78">
         <v>140280</v>
       </c>
       <c r="D78" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B79" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C79">
         <v>140290</v>
       </c>
       <c r="D79" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B80" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C80">
         <v>140300</v>
       </c>
       <c r="D80" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B81" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C81">
         <v>140310</v>
       </c>
       <c r="D81" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/#ZZZ.Skill.xlsx
+++ b/Configs/Datas/#ZZZ.Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC59AF70-3FD9-436F-A634-D34AE0B0251F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C8D398-DB55-4503-B84A-BEB4D849F13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="84">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -85,9 +85,6 @@
     <t>星见雅</t>
   </si>
   <si>
-    <t>艾莲乔</t>
-  </si>
-  <si>
     <t>基础_待机</t>
   </si>
   <si>
@@ -300,6 +297,26 @@
   </si>
   <si>
     <t>(list),ZZZ.AttributeCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_普通攻击_霜降</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_普通攻击_冰刃浪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_FlashFreeze,GreaterEqual,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_FlashFreeze,FixedValue,2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -664,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="29.375" customWidth="1"/>
@@ -678,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -690,10 +707,10 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" t="s">
         <v>73</v>
-      </c>
-      <c r="G1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -710,10 +727,10 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -738,7 +755,7 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
@@ -752,7 +769,7 @@
         <v>10000</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -763,7 +780,7 @@
         <v>10001</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -774,7 +791,7 @@
         <v>10002</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -785,7 +802,7 @@
         <v>10003</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -796,7 +813,7 @@
         <v>10004</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -807,7 +824,7 @@
         <v>10005</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -818,7 +835,7 @@
         <v>10006</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -829,7 +846,7 @@
         <v>10007</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -840,7 +857,7 @@
         <v>10008</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -851,7 +868,7 @@
         <v>10009</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -862,7 +879,7 @@
         <v>10010</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -873,7 +890,7 @@
         <v>10011</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
@@ -884,7 +901,7 @@
         <v>10012</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.2">
@@ -895,7 +912,7 @@
         <v>10013</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.2">
@@ -906,7 +923,7 @@
         <v>10014</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
@@ -917,7 +934,7 @@
         <v>10015</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
@@ -928,7 +945,7 @@
         <v>10016</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
@@ -939,7 +956,7 @@
         <v>10017</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
@@ -950,7 +967,7 @@
         <v>10018</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.2">
@@ -961,7 +978,7 @@
         <v>10019</v>
       </c>
       <c r="D24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.2">
@@ -972,7 +989,7 @@
         <v>10020</v>
       </c>
       <c r="D25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.2">
@@ -983,7 +1000,7 @@
         <v>10021</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.2">
@@ -994,7 +1011,7 @@
         <v>10022</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.2">
@@ -1005,7 +1022,7 @@
         <v>10023</v>
       </c>
       <c r="D28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.2">
@@ -1016,7 +1033,7 @@
         <v>10200</v>
       </c>
       <c r="D29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.2">
@@ -1027,7 +1044,7 @@
         <v>10201</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.2">
@@ -1038,7 +1055,7 @@
         <v>10202</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.2">
@@ -1049,7 +1066,7 @@
         <v>10203</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.2">
@@ -1060,7 +1077,7 @@
         <v>10204</v>
       </c>
       <c r="D33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
@@ -1071,7 +1088,7 @@
         <v>10205</v>
       </c>
       <c r="D34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.2">
@@ -1082,7 +1099,7 @@
         <v>10206</v>
       </c>
       <c r="D35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.2">
@@ -1093,7 +1110,7 @@
         <v>10207</v>
       </c>
       <c r="D36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.2">
@@ -1104,7 +1121,7 @@
         <v>10208</v>
       </c>
       <c r="D37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.2">
@@ -1115,7 +1132,7 @@
         <v>10209</v>
       </c>
       <c r="D38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.2">
@@ -1126,7 +1143,7 @@
         <v>10210</v>
       </c>
       <c r="D39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.2">
@@ -1137,7 +1154,7 @@
         <v>10211</v>
       </c>
       <c r="D40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.2">
@@ -1148,7 +1165,7 @@
         <v>10212</v>
       </c>
       <c r="D41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.2">
@@ -1159,7 +1176,7 @@
         <v>10213</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.2">
@@ -1170,7 +1187,7 @@
         <v>10214</v>
       </c>
       <c r="D43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.2">
@@ -1181,7 +1198,7 @@
         <v>10215</v>
       </c>
       <c r="D44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.2">
@@ -1192,7 +1209,7 @@
         <v>10216</v>
       </c>
       <c r="D45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.2">
@@ -1203,7 +1220,7 @@
         <v>10217</v>
       </c>
       <c r="D46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.2">
@@ -1214,7 +1231,7 @@
         <v>10218</v>
       </c>
       <c r="D47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.2">
@@ -1225,7 +1242,7 @@
         <v>10219</v>
       </c>
       <c r="D48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.2">
@@ -1236,389 +1253,417 @@
         <v>10220</v>
       </c>
       <c r="D49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C50">
         <v>140000</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C51">
         <v>140010</v>
       </c>
       <c r="D51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C52">
         <v>140020</v>
       </c>
       <c r="D52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C53">
         <v>140030</v>
       </c>
       <c r="D53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C54">
         <v>140040</v>
       </c>
       <c r="D54" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C55">
         <v>140050</v>
       </c>
       <c r="D55" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>140060</v>
       </c>
       <c r="D56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C57">
         <v>140070</v>
       </c>
       <c r="D57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C58">
         <v>140080</v>
       </c>
       <c r="D58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C59">
         <v>140090</v>
       </c>
       <c r="D59" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C60">
         <v>140100</v>
       </c>
       <c r="D60" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C61">
         <v>140110</v>
       </c>
       <c r="D61" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C62">
         <v>140120</v>
       </c>
       <c r="D62" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C63">
         <v>140130</v>
       </c>
       <c r="D63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C64">
         <v>140140</v>
       </c>
       <c r="D64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C65">
         <v>140150</v>
       </c>
       <c r="D65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C66">
         <v>140160</v>
       </c>
       <c r="D66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C67">
         <v>140170</v>
       </c>
       <c r="D67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C68">
         <v>140180</v>
       </c>
       <c r="D68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C69">
         <v>140190</v>
       </c>
       <c r="D69" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C70">
         <v>140200</v>
       </c>
       <c r="D70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F70" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G70" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C71">
         <v>140210</v>
       </c>
       <c r="D71" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G71" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C72">
         <v>140220</v>
       </c>
       <c r="D72" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F72" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C73">
         <v>140230</v>
       </c>
       <c r="D73" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C74">
         <v>140240</v>
       </c>
       <c r="D74" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F74" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G74" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C75">
         <v>140250</v>
       </c>
       <c r="D75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F75" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C76">
         <v>140260</v>
       </c>
       <c r="D76" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B77" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C77">
         <v>140270</v>
       </c>
       <c r="D77" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C78">
         <v>140280</v>
       </c>
       <c r="D78" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B79" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C79">
         <v>140290</v>
       </c>
       <c r="D79" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B80" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C80">
         <v>140300</v>
       </c>
       <c r="D80" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="81" spans="2:4" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B81" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C81">
         <v>140310</v>
       </c>
       <c r="D81" t="s">
-        <v>66</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B82" t="s">
+        <v>79</v>
+      </c>
+      <c r="C82">
+        <v>140320</v>
+      </c>
+      <c r="D82" t="s">
+        <v>81</v>
+      </c>
+      <c r="F82" t="s">
+        <v>82</v>
+      </c>
+      <c r="G82" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B83" t="s">
+        <v>79</v>
+      </c>
+      <c r="C83">
+        <v>140330</v>
+      </c>
+      <c r="D83" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/#ZZZ.Skill.xlsx
+++ b/Configs/Datas/#ZZZ.Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C8D398-DB55-4503-B84A-BEB4D849F13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92B276C-7741-4B04-979E-0E5BB7963E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="87">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -317,6 +317,18 @@
   </si>
   <si>
     <t>Ellen_FlashFreeze,FixedValue,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_招架支援_Start</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_招架支援_H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_招架支援_H_End</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -681,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="29.375" customWidth="1"/>
@@ -1666,6 +1678,39 @@
         <v>80</v>
       </c>
     </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B84" t="s">
+        <v>79</v>
+      </c>
+      <c r="C84">
+        <v>140340</v>
+      </c>
+      <c r="D84" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B85" t="s">
+        <v>79</v>
+      </c>
+      <c r="C85">
+        <v>140350</v>
+      </c>
+      <c r="D85" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B86" t="s">
+        <v>79</v>
+      </c>
+      <c r="C86">
+        <v>140360</v>
+      </c>
+      <c r="D86" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
